--- a/data/trans_orig/P36B07-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B07-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de zumo natural de frutas o verduras en 2016</t>
+          <t>Población según la frecuencia de consumo de zumo natural de frutas o verduras en 2016 (tasa de respuesta: 99,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80538</t>
+          <t>79086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114685</t>
+          <t>111527</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65231</t>
+          <t>64645</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96589</t>
+          <t>94977</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>154230</t>
+          <t>152651</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>198244</t>
+          <t>199366</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22190</t>
+          <t>22962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44180</t>
+          <t>46107</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23539</t>
+          <t>23862</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46403</t>
+          <t>47443</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50535</t>
+          <t>51454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81629</t>
+          <t>80606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48229</t>
+          <t>48781</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77746</t>
+          <t>78622</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37026</t>
+          <t>37331</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62688</t>
+          <t>63222</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>93329</t>
+          <t>91861</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>133215</t>
+          <t>130502</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35802</t>
+          <t>35682</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61469</t>
+          <t>61864</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39739</t>
+          <t>39282</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65549</t>
+          <t>66578</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81885</t>
+          <t>81272</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120095</t>
+          <t>120724</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39664</t>
+          <t>39757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68042</t>
+          <t>66795</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56628</t>
+          <t>56186</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84302</t>
+          <t>85284</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103840</t>
+          <t>103613</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143535</t>
+          <t>144281</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110102</t>
+          <t>108428</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149011</t>
+          <t>146998</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101361</t>
+          <t>102532</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140907</t>
+          <t>141223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>219950</t>
+          <t>220921</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>276871</t>
+          <t>278254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90372</t>
+          <t>90156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128729</t>
+          <t>128835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84926</t>
+          <t>85422</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122673</t>
+          <t>122674</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>187446</t>
+          <t>186612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>239795</t>
+          <t>236812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80994</t>
+          <t>81240</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116257</t>
+          <t>116934</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79893</t>
+          <t>80903</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115323</t>
+          <t>117827</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>168893</t>
+          <t>169537</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>220679</t>
+          <t>220683</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59419</t>
+          <t>60706</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92375</t>
+          <t>93978</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72252</t>
+          <t>72487</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105441</t>
+          <t>108226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>140711</t>
+          <t>145181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189570</t>
+          <t>194321</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70282</t>
+          <t>70193</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105570</t>
+          <t>106048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93436</t>
+          <t>92743</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132730</t>
+          <t>131384</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>174974</t>
+          <t>174181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227310</t>
+          <t>225448</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79989</t>
+          <t>80807</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112063</t>
+          <t>111131</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92903</t>
+          <t>92539</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125962</t>
+          <t>124857</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>181467</t>
+          <t>184994</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228929</t>
+          <t>230043</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99382</t>
+          <t>99026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131255</t>
+          <t>132883</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75172</t>
+          <t>75561</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>108175</t>
+          <t>105726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>184087</t>
+          <t>181132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227795</t>
+          <t>228249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52831</t>
+          <t>52713</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80732</t>
+          <t>81657</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65679</t>
+          <t>65139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>96736</t>
+          <t>96962</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>126810</t>
+          <t>126704</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>169471</t>
+          <t>164900</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13973</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31439</t>
+          <t>31207</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22161</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46273</t>
+          <t>44836</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40318</t>
+          <t>41763</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68632</t>
+          <t>70392</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>30858</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34044</t>
+          <t>35187</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32905</t>
+          <t>33168</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59569</t>
+          <t>58884</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>125371</t>
+          <t>125934</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163677</t>
+          <t>163800</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>135127</t>
+          <t>135020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173421</t>
+          <t>175515</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>269658</t>
+          <t>270646</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>326658</t>
+          <t>329302</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48541</t>
+          <t>48038</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>78593</t>
+          <t>79141</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>56417</t>
+          <t>54630</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>86716</t>
+          <t>85855</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>111444</t>
+          <t>113565</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>156153</t>
+          <t>155591</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48031</t>
+          <t>48992</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>78255</t>
+          <t>76440</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39598</t>
+          <t>40298</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>66846</t>
+          <t>68415</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>95043</t>
+          <t>94792</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>135849</t>
+          <t>135025</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17782</t>
+          <t>17541</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37857</t>
+          <t>38011</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18413</t>
+          <t>18444</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39849</t>
+          <t>39551</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40554</t>
+          <t>40687</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69961</t>
+          <t>70042</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57346</t>
+          <t>57668</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>90452</t>
+          <t>87732</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65580</t>
+          <t>65709</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>98331</t>
+          <t>99827</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>132205</t>
+          <t>133035</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>178088</t>
+          <t>176052</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12251</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17702</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24361</t>
+          <t>24657</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23121</t>
+          <t>22243</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>44075</t>
+          <t>43984</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22539</t>
+          <t>22830</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>42798</t>
+          <t>45301</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49818</t>
+          <t>51356</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>79938</t>
+          <t>79880</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42597</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>68372</t>
+          <t>68124</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>39228</t>
+          <t>39385</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62869</t>
+          <t>64310</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>88986</t>
+          <t>88552</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>122588</t>
+          <t>123806</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>61708</t>
+          <t>62600</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>89130</t>
+          <t>90274</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>66027</t>
+          <t>65378</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>94498</t>
+          <t>93800</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>135555</t>
+          <t>135418</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>174206</t>
+          <t>172323</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31460</t>
+          <t>32496</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>56012</t>
+          <t>55913</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>34451</t>
+          <t>35712</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>58201</t>
+          <t>59245</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>73796</t>
+          <t>73239</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>106112</t>
+          <t>106195</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>138167</t>
+          <t>139213</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>170851</t>
+          <t>170948</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>132751</t>
+          <t>132680</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>167386</t>
+          <t>165346</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>279617</t>
+          <t>281517</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>327840</t>
+          <t>326437</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>60,99%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>18227</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>38168</t>
+          <t>39252</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>21077</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>40718</t>
+          <t>41221</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>44530</t>
+          <t>43067</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>74216</t>
+          <t>73387</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>25005</t>
+          <t>24765</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46363</t>
+          <t>46539</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,49 +4381,49 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
+          <t>17,75%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>35533</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>25328</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>48308</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>13,01%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
           <t>17,69%</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>35533</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>24576</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>48681</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>13,01%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>17,82%</t>
-        </is>
-      </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
           <t>70</t>
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>54491</t>
+          <t>55495</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>85774</t>
+          <t>88085</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17891</t>
+          <t>17855</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>36840</t>
+          <t>37482</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>19328</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>37681</t>
+          <t>38212</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>41377</t>
+          <t>40259</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>68798</t>
+          <t>67346</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>11146</t>
+          <t>11666</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>29201</t>
+          <t>29106</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>22373</t>
+          <t>21323</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>43484</t>
+          <t>42199</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>37766</t>
+          <t>37683</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>66485</t>
+          <t>65550</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>110257</t>
+          <t>110547</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>151824</t>
+          <t>151150</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>131293</t>
+          <t>130638</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>175103</t>
+          <t>176553</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>252815</t>
+          <t>257035</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>313576</t>
+          <t>317085</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>106309</t>
+          <t>106166</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>149147</t>
+          <t>147178</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>112696</t>
+          <t>114230</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>153867</t>
+          <t>154691</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>230877</t>
+          <t>227118</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>288855</t>
+          <t>289521</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>135484</t>
+          <t>133102</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>181468</t>
+          <t>178934</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>138009</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>186600</t>
+          <t>183719</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>287001</t>
+          <t>286467</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>351339</t>
+          <t>350036</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>85771</t>
+          <t>84812</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>126221</t>
+          <t>127235</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>88039</t>
+          <t>87736</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>125960</t>
+          <t>126972</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>182097</t>
+          <t>184667</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>239642</t>
+          <t>239302</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>107157</t>
+          <t>107715</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>149168</t>
+          <t>151018</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>108414</t>
+          <t>108004</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>149643</t>
+          <t>151203</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>231825</t>
+          <t>230030</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>290997</t>
+          <t>289700</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>55417</t>
+          <t>55943</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>86634</t>
+          <t>88570</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,47 +5519,47 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>58782</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>44597</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>76051</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
           <t>7,18%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>58782</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>44861</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>75958</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
-        </is>
-      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>108625</t>
+          <t>109291</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>152677</t>
+          <t>153018</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>112090</t>
+          <t>112537</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>151852</t>
+          <t>151559</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>128146</t>
+          <t>126764</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>172949</t>
+          <t>172591</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>250958</t>
+          <t>250322</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>312904</t>
+          <t>311681</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>167750</t>
+          <t>165268</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>214754</t>
+          <t>212802</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>196047</t>
+          <t>195674</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>249070</t>
+          <t>248618</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>375816</t>
+          <t>376648</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>449860</t>
+          <t>447766</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>206300</t>
+          <t>201558</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>256703</t>
+          <t>254200</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>203325</t>
+          <t>202117</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>251800</t>
+          <t>257566</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>422681</t>
+          <t>420674</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>493652</t>
+          <t>493840</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>130005</t>
+          <t>130140</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>174558</t>
+          <t>178074</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>140320</t>
+          <t>139644</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>185298</t>
+          <t>187357</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>279238</t>
+          <t>281849</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>348732</t>
+          <t>346090</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>775499</t>
+          <t>776595</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>878716</t>
+          <t>876645</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>787647</t>
+          <t>783952</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>888042</t>
+          <t>884012</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1586906</t>
+          <t>1593063</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1726097</t>
+          <t>1726593</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>589303</t>
+          <t>591922</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>682242</t>
+          <t>683327</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>593346</t>
+          <t>590805</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>689326</t>
+          <t>686741</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1208315</t>
+          <t>1211457</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1336252</t>
+          <t>1336381</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>677767</t>
+          <t>672162</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>774753</t>
+          <t>770752</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>696186</t>
+          <t>699403</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>798057</t>
+          <t>796983</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1407294</t>
+          <t>1398045</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1542958</t>
+          <t>1537869</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>565913</t>
+          <t>563536</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>653903</t>
+          <t>655116</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>593804</t>
+          <t>593319</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>688247</t>
+          <t>685737</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1180480</t>
+          <t>1188773</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1311687</t>
+          <t>1323789</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>529160</t>
+          <t>531729</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>617529</t>
+          <t>622322</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>608648</t>
+          <t>609319</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>702763</t>
+          <t>704789</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1169030</t>
+          <t>1161420</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1297017</t>
+          <t>1295944</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B07-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B07-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79086</t>
+          <t>78987</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111527</t>
+          <t>112754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64645</t>
+          <t>65570</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94977</t>
+          <t>97219</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>152651</t>
+          <t>151754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199366</t>
+          <t>197848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,38%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22962</t>
+          <t>22942</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46107</t>
+          <t>46195</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23862</t>
+          <t>23577</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47443</t>
+          <t>46757</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51454</t>
+          <t>50105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80606</t>
+          <t>81609</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48781</t>
+          <t>48938</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78622</t>
+          <t>78586</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37331</t>
+          <t>36840</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63222</t>
+          <t>63435</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91861</t>
+          <t>93678</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>130502</t>
+          <t>132817</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35682</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61864</t>
+          <t>61207</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39282</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66578</t>
+          <t>67580</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81272</t>
+          <t>81305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120724</t>
+          <t>119556</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39757</t>
+          <t>39560</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66795</t>
+          <t>67710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>57340</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85284</t>
+          <t>86713</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103613</t>
+          <t>103291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>144281</t>
+          <t>143019</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108428</t>
+          <t>108618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146998</t>
+          <t>148078</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102532</t>
+          <t>100539</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141223</t>
+          <t>140290</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,47 +1462,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>26,89%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>247603</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>221175</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>276148</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>21,68%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>27,07%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>247603</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>220921</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>278254</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>21,66%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90156</t>
+          <t>89081</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128835</t>
+          <t>128013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85422</t>
+          <t>84618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122674</t>
+          <t>121690</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>186612</t>
+          <t>187441</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>236812</t>
+          <t>240757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81240</t>
+          <t>80774</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116934</t>
+          <t>115210</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80903</t>
+          <t>80533</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117827</t>
+          <t>117145</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>169537</t>
+          <t>169468</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>220683</t>
+          <t>221006</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60706</t>
+          <t>60334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93978</t>
+          <t>92658</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72487</t>
+          <t>71868</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108226</t>
+          <t>109781</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145181</t>
+          <t>145489</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194321</t>
+          <t>190390</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70193</t>
+          <t>71418</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106048</t>
+          <t>105882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92743</t>
+          <t>93726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131384</t>
+          <t>133491</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>174181</t>
+          <t>176319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225448</t>
+          <t>226310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80807</t>
+          <t>78787</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111131</t>
+          <t>110205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92539</t>
+          <t>92064</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124857</t>
+          <t>127542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>184994</t>
+          <t>181493</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>230043</t>
+          <t>226682</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99026</t>
+          <t>99761</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132883</t>
+          <t>131467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75561</t>
+          <t>74396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105726</t>
+          <t>106357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181132</t>
+          <t>181518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>228249</t>
+          <t>230478</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>52285</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81657</t>
+          <t>80920</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65139</t>
+          <t>64364</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>96962</t>
+          <t>96939</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>126704</t>
+          <t>127461</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>164900</t>
+          <t>167520</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31207</t>
+          <t>32121</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21619</t>
+          <t>22480</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44836</t>
+          <t>45384</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41763</t>
+          <t>41300</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70392</t>
+          <t>70564</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30858</t>
+          <t>31462</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35187</t>
+          <t>35052</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33168</t>
+          <t>32667</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58884</t>
+          <t>59668</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>125934</t>
+          <t>125864</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163800</t>
+          <t>163639</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>135020</t>
+          <t>134911</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>175515</t>
+          <t>176024</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>270646</t>
+          <t>271153</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>329302</t>
+          <t>329625</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48038</t>
+          <t>48654</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>79141</t>
+          <t>78045</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>54630</t>
+          <t>55133</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>85855</t>
+          <t>86967</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>113565</t>
+          <t>110488</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>155591</t>
+          <t>154141</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48992</t>
+          <t>46723</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76440</t>
+          <t>75304</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40298</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>68415</t>
+          <t>67984</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>94792</t>
+          <t>94087</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>135025</t>
+          <t>135396</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17541</t>
+          <t>17173</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38011</t>
+          <t>36963</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18444</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39551</t>
+          <t>38966</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40687</t>
+          <t>40368</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70042</t>
+          <t>67520</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57668</t>
+          <t>56447</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>87732</t>
+          <t>89395</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65709</t>
+          <t>66602</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>99827</t>
+          <t>99409</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>133035</t>
+          <t>130060</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>176052</t>
+          <t>174594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9788</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24657</t>
+          <t>25574</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22243</t>
+          <t>23603</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>43984</t>
+          <t>43912</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22830</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45301</t>
+          <t>43089</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>51356</t>
+          <t>49427</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>79880</t>
+          <t>78388</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42681</t>
+          <t>41909</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>68124</t>
+          <t>67097</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>39385</t>
+          <t>38453</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>64310</t>
+          <t>63318</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>88552</t>
+          <t>86548</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>123806</t>
+          <t>122261</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>62600</t>
+          <t>62482</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>90274</t>
+          <t>89073</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>65378</t>
+          <t>66019</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>93800</t>
+          <t>92769</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>135418</t>
+          <t>136416</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>172323</t>
+          <t>176332</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>31541</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>55913</t>
+          <t>55029</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>35712</t>
+          <t>35177</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>59245</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>73239</t>
+          <t>73929</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>106195</t>
+          <t>105637</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>139213</t>
+          <t>137517</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>170948</t>
+          <t>170958</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>132680</t>
+          <t>133154</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>165346</t>
+          <t>166696</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>281517</t>
+          <t>282092</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>326437</t>
+          <t>326247</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,95%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18227</t>
+          <t>18335</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>39252</t>
+          <t>38256</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19955</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>41221</t>
+          <t>42040</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>43067</t>
+          <t>43555</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>73387</t>
+          <t>74041</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>24765</t>
+          <t>23867</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46539</t>
+          <t>46098</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>25328</t>
+          <t>24738</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>48308</t>
+          <t>48424</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>55495</t>
+          <t>55969</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>88085</t>
+          <t>86517</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17855</t>
+          <t>17152</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>37482</t>
+          <t>37172</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>18847</t>
+          <t>18404</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>38212</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>40259</t>
+          <t>42791</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>67346</t>
+          <t>69443</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>11666</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>29106</t>
+          <t>29169</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>21323</t>
+          <t>22323</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>42199</t>
+          <t>44300</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>37683</t>
+          <t>37689</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>65550</t>
+          <t>65700</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>110547</t>
+          <t>109680</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>151150</t>
+          <t>153693</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>130638</t>
+          <t>131736</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>176553</t>
+          <t>176240</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>257035</t>
+          <t>251875</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>317085</t>
+          <t>311800</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>106166</t>
+          <t>104457</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>147178</t>
+          <t>149198</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>114230</t>
+          <t>112530</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>154691</t>
+          <t>155387</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>227118</t>
+          <t>229600</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>289521</t>
+          <t>290898</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>133102</t>
+          <t>134343</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>178934</t>
+          <t>180010</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>138009</t>
+          <t>136109</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>183719</t>
+          <t>183661</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>286467</t>
+          <t>287860</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>350036</t>
+          <t>351756</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>84812</t>
+          <t>83595</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>127235</t>
+          <t>125367</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>87736</t>
+          <t>89660</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>126972</t>
+          <t>130382</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>184667</t>
+          <t>181535</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>239302</t>
+          <t>237657</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>107715</t>
+          <t>107870</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>151018</t>
+          <t>150536</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>108004</t>
+          <t>110140</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>151203</t>
+          <t>151443</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>230030</t>
+          <t>229152</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>289700</t>
+          <t>290539</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>55943</t>
+          <t>56255</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>88570</t>
+          <t>87533</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>44597</t>
+          <t>45048</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>76051</t>
+          <t>75307</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>109291</t>
+          <t>106811</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>153018</t>
+          <t>154216</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>112537</t>
+          <t>110695</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>151559</t>
+          <t>152920</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>126764</t>
+          <t>125829</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>172591</t>
+          <t>171922</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>250322</t>
+          <t>247905</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>311681</t>
+          <t>307963</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>165268</t>
+          <t>166846</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>212802</t>
+          <t>212910</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>195674</t>
+          <t>195607</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>248618</t>
+          <t>246613</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>376648</t>
+          <t>372381</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>447766</t>
+          <t>444498</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>201558</t>
+          <t>204814</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>254200</t>
+          <t>254387</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>202117</t>
+          <t>203433</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>257566</t>
+          <t>255560</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>420674</t>
+          <t>420079</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>493840</t>
+          <t>495404</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>130140</t>
+          <t>129563</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>178074</t>
+          <t>174178</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>139644</t>
+          <t>140033</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>187357</t>
+          <t>186316</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>281849</t>
+          <t>281267</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>346090</t>
+          <t>345780</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>776595</t>
+          <t>775157</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>876645</t>
+          <t>872957</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>783952</t>
+          <t>778738</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>884012</t>
+          <t>880635</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1593063</t>
+          <t>1581904</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1726593</t>
+          <t>1736188</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>591922</t>
+          <t>587945</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>683327</t>
+          <t>679092</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>590805</t>
+          <t>599802</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>686741</t>
+          <t>690104</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1211457</t>
+          <t>1208763</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1336381</t>
+          <t>1341339</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>672162</t>
+          <t>678100</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>770752</t>
+          <t>774882</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>699403</t>
+          <t>699012</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>796983</t>
+          <t>796669</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1398045</t>
+          <t>1403557</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1537869</t>
+          <t>1537875</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>563536</t>
+          <t>567732</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>655116</t>
+          <t>654526</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>593319</t>
+          <t>596082</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>685737</t>
+          <t>688363</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1188773</t>
+          <t>1185035</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1323789</t>
+          <t>1318546</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>531729</t>
+          <t>531216</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>622322</t>
+          <t>619386</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>609319</t>
+          <t>612804</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>704789</t>
+          <t>705048</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1161420</t>
+          <t>1168449</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1295944</t>
+          <t>1299154</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
